--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:26</t>
+    <t xml:space="preserve">2026-09-10 01:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:41</t>
+    <t xml:space="preserve">2026-09-18 11:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:37</t>
+    <t xml:space="preserve">2026-09-23 15:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:42</t>
+    <t xml:space="preserve">2026-10-05 16:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1409,7 +1409,7 @@
         <v>104.72</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>64.97</v>
+        <v>64.98</v>
       </c>
     </row>
     <row r="31">
